--- a/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
+++ b/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>The role is guessed when unclear and recorded on Summary. The skill never stops to ask.</t>
+          <t>The role is guessed when unclear and recorded on Summary. The only time the skill asks is when a name containing 'Start2' other than Start2 Asia appears: it flags the name and waits for confirmation.</t>
         </is>
       </c>
     </row>

--- a/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
+++ b/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Produced by the contract review skill from the contract text and the Start2 standards workbook, then checked by a person. Counts and the recommendation update when you edit the Findings sheet.</t>
+          <t>Produced by the contract review skill from the contract text and the Start2 standards workbook, then checked by a person. Counts and the to-confirm line update when you edit the Findings sheet.</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Read the role, the counts and the recommendation. Check the role guess first: if it is wrong, nothing else applies.</t>
+          <t>Read the role, the counts and the number of findings to confirm. Check the role guess first: if it is wrong, nothing else applies.</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Do not sign (if already executed, escalate at once). Reject threshold met, hard stop, wrong entity, no liability cap, blank essential fields.</t>
+          <t>Do not sign as it stands. Reject threshold met, hard stop, wrong entity, no liability cap, blank essential fields.</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Provider, Buyer or Other. The standards cover provider-side contracts only. If the role is not Provider, standards coverage is not applied and the recommendation says so.</t>
+          <t>Provider, Buyer or Other. The standards cover provider-side contracts only. If the role is not Provider, standards coverage is not applied and the To confirm line says so.</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Recommendation</t>
+          <t>To confirm</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Formula. Draft: any Critical = Escalate; any High = Proceed with named conditions; otherwise Proceed. Executed: no signature gate; Critical items are escalated and High items logged for amendment or renewal.</t>
+          <t>Formula: the number of Critical and High findings. These are logged for a person to confirm; nothing else is recommended.</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Counts and the recommendation use the Findings sheet only. Coverage severity is a view and is not counted.</t>
+          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
         </is>
       </c>
     </row>
@@ -1423,11 +1423,11 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Recommendation</t>
+          <t>To confirm</t>
         </is>
       </c>
       <c r="B19" s="5">
-        <f>IF(OR(B5="",B11=""),"",IF(B11&lt;&gt;"Provider","Not assessed: the standards cover provider-side contracts only",IF(B5="Executed",IF(B15&gt;0,"Executed: escalate Critical items and log High items for amendment or renewal",IF(B16&gt;0,"Executed: log High items for amendment or renewal","Executed: no action required")),IF(B15&gt;0,"Escalate",IF(B16&gt;0,"Proceed with named conditions","Proceed")))))</f>
+        <f>IF(B11="","",IF(B11&lt;&gt;"Provider","Not assessed: the standards cover provider-side contracts only",(B15+B16)&amp;" Critical and High findings to confirm"))</f>
         <v/>
       </c>
       <c r="C19" s="5" t="n"/>

--- a/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
+++ b/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Findings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Coverage" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Checks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents not supplied" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Coverage'!$A$1:$G$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Documents not supplied'!$A$1:$H$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -574,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -670,505 +672,509 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5. Documents not supplied</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Every outside document the contract names (general conditions, bids, policies, codes, links) that was not supplied with it. Terms in these documents were not reviewed. Obtain them and re-run the review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Do not sign as it stands. Reject threshold met, hard stop, wrong entity, no liability cap, blank essential fields.</t>
-        </is>
-      </c>
+      <c r="B10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Fix, or have the full sign-off chain knowingly accept it, before signing. Material cash, liability, IP, data, forum or scope exposure.</t>
+          <t>Do not sign as it stands. Reject threshold met, hard stop, wrong entity, no liability cap, blank essential fields.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Should be fixed. Negotiable. Raises dispute risk but not direct cash loss.</t>
+          <t>Fix, or have the full sign-off chain knowingly accept it, before signing. Material cash, liability, IP, data, forum or scope exposure.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Should be fixed. Negotiable. Raises dispute risk but not direct cash loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Housekeeping, optional clauses, accepted client clauses.</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Summary (Item / Value / Where)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Subjective wording</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Name or title of the contract being reviewed.</t>
+          <t>A finding whose quoted text lets the counterparty alone judge Start2's work, payment or people (for example 'acceptable to Canada', 'to the satisfaction of', 'in its sole discretion') is raised one severity level and marked Yes in the Subjective column.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Source file</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>File name of the contract that was reviewed.</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Summary (Item / Value / Where)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Draft (unsigned) or Executed (signed). Executed contracts get remediation wording instead of sign/no-sign.</t>
+          <t>Name or title of the contract being reviewed.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Contract type</t>
+          <t>Source file</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Service, Funding, Vendor or Other. Funding agreements (grants, claims, audits) read the fee and cost clauses differently.</t>
+          <t>File name of the contract that was reviewed.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Whose paper</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Start2 template unmodified, Start2 template modified, or client or third-party paper. Sets the review lead time: 3 business days for the unmodified template, otherwise 5.</t>
+          <t>Draft (unsigned) or Executed (signed). Executed contracts get remediation wording instead of sign/no-sign.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Standards version</t>
+          <t>Contract type</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Version of the standards workbook the contract was checked against.</t>
+          <t>Service, Funding, Vendor or Other. Funding agreements (grants, claims, audits) read the fee and cost clauses differently.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Our entity</t>
+          <t>Whose paper</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>The Start2 entity in this contract. Guessed from the entity list and the text when not obvious.</t>
+          <t>Start2 template unmodified, Start2 template modified, or client or third-party paper. Sets the review lead time: 3 business days for the unmodified template, otherwise 5.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Our role</t>
+          <t>Standards version</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Provider, Buyer or Other. The standards cover provider-side contracts only. If the role is not Provider, standards coverage is not applied and the To confirm line says so.</t>
+          <t>Version of the standards workbook the contract was checked against.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Role basis</t>
+          <t>Our entity</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>One sentence on why that role was chosen. Always filled when the role was guessed.</t>
+          <t>The Start2 entity in this contract. Guessed from the entity list and the text when not obvious.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Counterparty</t>
+          <t>Our role</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>The other party.</t>
+          <t>Provider, Buyer or Other. The standards cover provider-side contracts only. If the role is not Provider, standards coverage is not applied and the To confirm line says so.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Critical / High / Medium / Low</t>
+          <t>Role basis</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Formulas: number of Findings at each severity.</t>
+          <t>One sentence on why that role was chosen. Always filled when the role was guessed.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Counterparty</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Formula: the number of Critical and High findings. These are logged for a person to confirm; nothing else is recommended.</t>
+          <t>The other party.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Review lead time</t>
+          <t>Critical / High / Medium / Low</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Formula from Whose paper.</t>
+          <t>Formulas: number of Findings at each severity.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Sign-off chain</t>
+          <t>To confirm</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Fixed. Every contract goes to all three approvers in order.</t>
+          <t>Formula: the number of Critical and High findings. These are logged for a person to confirm; nothing else is recommended.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Key facts (Fact / Value / Where)</t>
+          <t>Documents not supplied</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Facts used in the review: parties, dates, amounts, law, forum, language, annexes, with arithmetic checks. Where gives the contract reference and page.</t>
+          <t>Formula: the number of rows on the Documents not supplied sheet.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Findings (one row per issue)</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Review lead time</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Formula from Whose paper.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Sign-off chain</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Running number.</t>
+          <t>Fixed. Every contract goes to all three approvers in order.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Key facts (Fact / Value / Where)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Critical, High, Medium or Low (drop-down).</t>
+          <t>Facts used in the review: parties, dates, amounts, law, forum, language, annexes, with arithmetic checks. Where gives the contract reference and page.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Missing, Partial or Deviant (a standard clause); Client: Reject, Escalate, Conditional or Accept (a client-added clause matched to the playbook); Unclassified clause (not in the standard or playbook, generic screen); Commercial (fee, dates, arithmetic); Execution (a failed check); Other.</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Findings (one row per issue)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Clause</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Standard clause ID (for example LOL), the playbook row name, or Check n.</t>
+          <t>Running number.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Contract clause number and page, for example 13.1 (p. 10). 'Not in contract' for an absent clause.</t>
+          <t>Critical, High, Medium or Low (drop-down).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Verbatim text from the contract. Scanned contracts are transcribed from page images, so check the page before relying on a quote.</t>
+          <t>Missing, Partial or Deviant (a standard clause); Client: Reject, Escalate, Conditional or Accept (a client-added clause matched to the playbook); Unclassified clause (not in the standard or playbook, generic screen); Commercial (fee, dates, arithmetic); Execution (a failed check); Not supplied (a document that forms part of the contract was not supplied, so its terms were not reviewed); Other.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Clause</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>What is wrong and why it matters, against the standard.</t>
+          <t>Standard clause ID (for example LOL), the playbook row name, or Check n.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>What to do: insert, change, accept, escalate, or confirm.</t>
+          <t>Contract clause number and page, for example 13.1 (p. 10). 'Not in contract' for an absent clause.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Coverage (one row per standard clause)</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Verbatim text from the contract: the full sentence or sub-clause, with the words the finding turns on in bold. '...' marks text left out between excerpts. Scanned contracts are transcribed from page images, so check the page before relying on a quote.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Issue</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Stable clause key from the standards workbook.</t>
+          <t>What the clause says in plain words, what it means for Start2 in practice, how it compares with the Start2 standard, and why it has this severity.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Clause</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Clause name.</t>
+          <t>What to do next and who does it: what to check internally, what to ask the counterparty for, and a fallback if they decline.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Base severity</t>
+          <t>Suggested language</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Severity if the clause is missing or deviant. Editable for this contract (for example raise anti-bribery to Medium for a government counterparty). n/a for internal rules.</t>
+          <t>Wording to propose to the counterparty. For a standard clause, the Start2 standard language with the parties named as in this contract; otherwise wording written for this finding. Fill bracketed items and adjust before sending.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Verdict</t>
+          <t>Subjective</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Conforming, Partial, Deviant, Missing, or N/A (drop-down).</t>
+          <t>Yes when the quoted text lets the counterparty alone judge Start2's work, payment or people. The severity already includes the one-level raise.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Where</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Contract clause number and page where the clause was found.</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Coverage (one row per standard clause)</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Formula. Missing or Deviant = Base severity; Partial = one level lower (floor Low); Conforming or N/A = '-'.</t>
+          <t>Stable clause key from the standards workbook.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Clause</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>One line on what is present or absent. Details are in Findings.</t>
+          <t>Clause name.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Checks (one row per execution check)</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Base severity</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Severity if the clause is missing or deviant. Editable for this contract (for example raise anti-bribery to Medium for a government counterparty). n/a for internal rules.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Verdict</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Number of the check in the standards workbook.</t>
+          <t>Conforming, Partial, Deviant, Missing, Not supplied (the contract says the topic is governed by a document that was not supplied), or N/A (drop-down).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>What is verified before a draft leaves Start2 and again before signature.</t>
+          <t>Contract clause number and page where the clause was found.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Pass, Fail, N/A or Cannot verify (drop-down).</t>
+          <t>Formula. Missing, Deviant or Not supplied = Base severity; Partial = one level lower (floor Low); Conforming or N/A = '-'.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>What was seen, with page references.</t>
+          <t>One line on what is present or absent. Details are in Findings.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Sheet: Checks (one row per execution check)</t>
         </is>
       </c>
       <c r="B52" s="3" t="n"/>
@@ -1176,49 +1182,198 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Counts</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
+          <t>Number of the check in the standards workbook.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>The role is guessed when unclear and recorded on Summary. The only time the skill asks is when a name containing 'Start2' other than Start2 Asia appears: it flags the name and waits for confirmation.</t>
+          <t>What is verified before a draft leaves Start2 and again before signature.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Pass, Fail, N/A or Cannot verify (drop-down).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>What was seen, with page references.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Documents not supplied (one row per document)</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>The document as the contract names it, with version or date if given.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Referenced at</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Contract clause and page where it is named.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>The contract text that names or incorporates it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Part of contract</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Yes when the contract says the document applies to or forms part of the contract. Those also appear in Findings as type Not supplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Governs</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>What the contract says or shows the document covers. Never a guess at its content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Effect on this review</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Which findings and coverage rows could not be completed without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>How to obtain it and what to check once it is in hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>The role is guessed when unclear and recorded on Summary. The only time the skill asks is when a name containing 'Start2' other than Start2 Asia appears: it flags the name and waits for confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
           <t>Not legal advice</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>A screen against Start2 standards. Decisions follow the sign-off chain.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1230,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1435,11 +1590,11 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Review lead time</t>
+          <t>Documents not supplied</t>
         </is>
       </c>
       <c r="B20" s="5">
-        <f>IF(B7="","",IF(B7="Start2 template, unmodified","3 business days","5 business days"))</f>
+        <f>COUNTA('Documents not supplied'!$B$2:$B$300)</f>
         <v/>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -1447,24 +1602,36 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>Review lead time</t>
+        </is>
+      </c>
+      <c r="B21" s="5">
+        <f>IF(B7="","",IF(B7="Start2 template, unmodified","3 business days","5 business days"))</f>
+        <v/>
+      </c>
+      <c r="C21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>Sign-off chain</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>1. Director of People and Operations; 2. Regional Director of Innovation and Product Strategy; 3. CEO. Applies to every contract.</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="C22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Key facts</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A15:A18">
@@ -1505,7 +1672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1513,9 +1680,11 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1559,9 +1728,19 @@
           <t>Action</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Suggested language</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Subjective</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:J2"/>
   <conditionalFormatting sqref="B2:B300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Critical"</formula>
@@ -1576,12 +1755,15 @@
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Missing,Partial,Deviant,Client: Reject,Client: Escalate,Client: Conditional,Client: Accept,Unclassified clause,Commercial,Execution,Other"</formula1>
+      <formula1>"Missing,Partial,Deviant,Client: Reject,Client: Escalate,Client: Conditional,Client: Accept,Unclassified clause,Commercial,Execution,Not supplied,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2494,7 +2676,7 @@
       <formula1>"Critical,High,Medium,Low,n/a"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Conforming,Partial,Deviant,Missing,N/A"</formula1>
+      <formula1>"Conforming,Partial,Deviant,Missing,Not supplied,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2690,4 +2872,76 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Referenced at</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Quote</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Part of contract</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Governs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Effect on this review</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
+++ b/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents not supplied" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Coverage'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Documents not supplied'!$A$1:$H$2</definedName>
   </definedNames>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -742,622 +742,658 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>No action needed</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>A finding that needs nothing from Start2 beyond noting it is lowered one severity level and marked No in the Action needed column. Its Action explains why nothing is needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Subjective wording</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>A finding whose quoted text lets the counterparty alone judge Start2's work, payment or people (for example 'acceptable to Canada', 'to the satisfaction of', 'in its sole discretion') is raised one severity level and marked Yes in the Subjective column.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Sheet: Summary (Item / Value / Where)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Name or title of the contract being reviewed.</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Source file</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>File name of the contract that was reviewed.</t>
+          <t>Name or title of the contract being reviewed.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Source file</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Draft (unsigned) or Executed (signed). Executed contracts get remediation wording instead of sign/no-sign.</t>
+          <t>File name of the contract that was reviewed.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Contract type</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Service, Funding, Vendor or Other. Funding agreements (grants, claims, audits) read the fee and cost clauses differently.</t>
+          <t>Draft (unsigned) or Executed (signed). Executed contracts get remediation wording instead of sign/no-sign.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Whose paper</t>
+          <t>Contract type</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Start2 template unmodified, Start2 template modified, or client or third-party paper. Sets the review lead time: 3 business days for the unmodified template, otherwise 5.</t>
+          <t>Service, Funding, Vendor or Other. Funding agreements (grants, claims, audits) read the fee and cost clauses differently.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Standards version</t>
+          <t>Whose paper</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Version of the standards workbook the contract was checked against.</t>
+          <t>Start2 template unmodified, Start2 template modified, or client or third-party paper. Sets the review lead time: 3 business days for the unmodified template, otherwise 5.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Our entity</t>
+          <t>Standards version</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>The Start2 entity in this contract. Guessed from the entity list and the text when not obvious.</t>
+          <t>Version of the standards workbook the contract was checked against.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Our role</t>
+          <t>Our entity</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Provider, Buyer or Other. The standards cover provider-side contracts only. If the role is not Provider, standards coverage is not applied and the To confirm line says so.</t>
+          <t>The Start2 entity in this contract. Guessed from the entity list and the text when not obvious.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Role basis</t>
+          <t>Our role</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>One sentence on why that role was chosen. Always filled when the role was guessed.</t>
+          <t>Provider, Buyer or Other. The standards cover provider-side contracts only. If the role is not Provider, standards coverage is not applied and the To confirm line says so.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Counterparty</t>
+          <t>Role basis</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>The other party.</t>
+          <t>One sentence on why that role was chosen. Always filled when the role was guessed.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Critical / High / Medium / Low</t>
+          <t>Counterparty</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Formulas: number of Findings at each severity.</t>
+          <t>The other party.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Critical / High / Medium / Low</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Formula: the number of Critical and High findings. These are logged for a person to confirm; nothing else is recommended.</t>
+          <t>Formulas: number of Findings at each severity.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Documents not supplied</t>
+          <t>To confirm</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Formula: the number of rows on the Documents not supplied sheet.</t>
+          <t>Formula: the number of Critical and High findings. These are logged for a person to confirm; nothing else is recommended.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Review lead time</t>
+          <t>Documents not supplied</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Formula from Whose paper.</t>
+          <t>Formula: the number of rows on the Documents not supplied sheet.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Sign-off chain</t>
+          <t>Review lead time</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Fixed. Every contract goes to all three approvers in order.</t>
+          <t>Formula from Whose paper.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>Sign-off chain</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Fixed. Every contract goes to all three approvers in order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>Key facts (Fact / Value / Where)</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Facts used in the review: parties, dates, amounts, law, forum, language, annexes, with arithmetic checks. Where gives the contract reference and page.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sheet: Findings (one row per issue)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Running number.</t>
-        </is>
-      </c>
+      <c r="B34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Critical, High, Medium or Low (drop-down).</t>
+          <t>Running number.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Missing, Partial or Deviant (a standard clause); Client: Reject, Escalate, Conditional or Accept (a client-added clause matched to the playbook); Unclassified clause (not in the standard or playbook, generic screen); Commercial (fee, dates, arithmetic); Execution (a failed check); Not supplied (a document that forms part of the contract was not supplied, so its terms were not reviewed); Other.</t>
+          <t>Critical, High, Medium or Low (drop-down).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Clause</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Standard clause ID (for example LOL), the playbook row name, or Check n.</t>
+          <t>Missing, Partial or Deviant (a standard clause); Client: Reject, Escalate, Conditional or Accept (a client-added clause matched to the playbook); Unclassified clause (not in the standard or playbook, generic screen); Commercial (fee, dates, arithmetic); Execution (a failed check); Not supplied (a document that forms part of the contract was not supplied, so its terms were not reviewed); Other.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>Clause</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Contract clause number and page, for example 13.1 (p. 10). 'Not in contract' for an absent clause.</t>
+          <t>Standard clause ID (for example LOL), the playbook row name, or Check n.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Verbatim text from the contract: the full sentence or sub-clause, with the words the finding turns on in bold. '...' marks text left out between excerpts. Scanned contracts are transcribed from page images, so check the page before relying on a quote.</t>
+          <t>Contract clause number and page, for example 13.1 (p. 10). 'Not in contract' for an absent clause.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>What the clause says in plain words, what it means for Start2 in practice, how it compares with the Start2 standard, and why it has this severity.</t>
+          <t>Verbatim text from the contract: the full sentence or sub-clause, with the words the finding turns on in bold. '...' marks text left out between excerpts. Scanned contracts are transcribed from page images, so check the page before relying on a quote.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Issue</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>What to do next and who does it: what to check internally, what to ask the counterparty for, and a fallback if they decline.</t>
+          <t>What the clause says in plain words, what it means for Start2 in practice, how it compares with the Start2 standard, and why it has this severity.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Suggested language</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Wording to propose to the counterparty. For a standard clause, the Start2 standard language with the parties named as in this contract; otherwise wording written for this finding. Fill bracketed items and adjust before sending.</t>
+          <t>What to do next and who does it: what to check internally, what to ask the counterparty for, and a fallback if they decline.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t>Suggested language</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Wording to propose to the counterparty. For a standard clause, the Start2 standard language with the parties named as in this contract; otherwise wording written for this finding. Fill bracketed items and adjust before sending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>Subjective</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Yes when the quoted text lets the counterparty alone judge Start2's work, payment or people. The severity already includes the one-level raise.</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Coverage (one row per standard clause)</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Action needed</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Stable clause key from the standards workbook.</t>
+          <t>No when the finding needs nothing beyond noting it. The severity already includes the one-level reduction.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Clause</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Clause name.</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Coverage (one row per standard clause)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Base severity</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Severity if the clause is missing or deviant. Editable for this contract (for example raise anti-bribery to Medium for a government counterparty). n/a for internal rules.</t>
+          <t>Stable clause key from the standards workbook.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Verdict</t>
+          <t>Clause</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Conforming, Partial, Deviant, Missing, Not supplied (the contract says the topic is governed by a document that was not supplied), or N/A (drop-down).</t>
+          <t>Clause name.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>Base severity</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Contract clause number and page where the clause was found.</t>
+          <t>Severity if the clause is missing or deviant. Editable for this contract (for example raise anti-bribery to Medium for a government counterparty). n/a for internal rules.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Verdict</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Formula. Missing, Deviant or Not supplied = Base severity; Partial = one level lower (floor Low); Conforming or N/A = '-'.</t>
+          <t>Conforming, Partial, Deviant, Missing, Not supplied (the contract says the topic is governed by a document that was not supplied), or N/A (drop-down).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>One line on what is present or absent. Details are in Findings.</t>
+          <t>Contract clause number and page where the clause was found.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Checks (one row per execution check)</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n"/>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Formula. Missing, Deviant or Not supplied = Base severity; Partial = one level lower (floor Low); Conforming or N/A = '-'.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Number of the check in the standards workbook.</t>
+          <t>One line on what is present or absent. Details are in Findings.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>What is verified before a draft leaves Start2 and again before signature.</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Checks (one row per execution check)</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Pass, Fail, N/A or Cannot verify (drop-down).</t>
+          <t>Number of the check in the standards workbook.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>What was seen, with page references.</t>
+          <t>What is verified before a draft leaves Start2 and again before signature.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Documents not supplied (one row per document)</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n"/>
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Pass, Fail, N/A or Cannot verify (drop-down).</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>The document as the contract names it, with version or date if given.</t>
+          <t>What was seen, with page references.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Referenced at</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Contract clause and page where it is named.</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Documents not supplied (one row per document)</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>The contract text that names or incorporates it.</t>
+          <t>The document as the contract names it, with version or date if given.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Part of contract</t>
+          <t>Referenced at</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Yes when the contract says the document applies to or forms part of the contract. Those also appear in Findings as type Not supplied.</t>
+          <t>Every contract clause and page where the document is named, numbered.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Governs</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>What the contract says or shows the document covers. Never a guess at its content.</t>
+          <t>The contract text at each of those places, numbered to match, with the document's name in bold.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Effect on this review</t>
+          <t>Part of contract</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Which findings and coverage rows could not be completed without it.</t>
+          <t>Yes when the contract says the document applies to or forms part of the contract. Those also appear in Findings as type Not supplied.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Governs</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>How to obtain it and what to check once it is in hand.</t>
+          <t>What the contract says or shows the document covers. Never a guess at its content.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Rules</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n"/>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Effect on this review</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Which findings and coverage rows could not be completed without it.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Counts</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
+          <t>How to obtain it and what to check once it is in hand.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
+          <t>Terms used</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Where a legal term or a Start2 clause code (for example WARR) is used without explanation, a 'Terms used' line at the end of the cell gives its plain meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>The role is guessed when unclear and recorded on Summary. The only time the skill asks is when a name containing 'Start2' other than Start2 Asia appears: it flags the name and waits for confirmation.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Not legal advice</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>A screen against Start2 standards. Decisions follow the sign-off chain.</t>
         </is>
@@ -1366,14 +1402,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1672,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1685,6 +1721,7 @@
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1738,9 +1775,14 @@
           <t>Subjective</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Action needed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J2"/>
+  <autoFilter ref="A1:K2"/>
   <conditionalFormatting sqref="B2:B300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Critical"</formula>
@@ -1755,7 +1797,7 @@
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
@@ -1764,6 +1806,9 @@
     </dataValidation>
     <dataValidation sqref="J2:J300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2885,8 +2930,8 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
@@ -2911,7 +2956,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">

--- a/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
+++ b/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -834,566 +834,590 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Standards version</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Version of the standards workbook the contract was checked against.</t>
+          <t>Pre-signature (findings are requests before signing), Signed (checks and records for the current contract) or Renewal (requests for the next version). Confirmed with the requester before the review starts.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Our entity</t>
+          <t>Standards version</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>The Start2 entity in this contract. Guessed from the entity list and the text when not obvious.</t>
+          <t>Version of the standards workbook the contract was checked against.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Our role</t>
+          <t>Our entity</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Provider, Buyer or Other. The standards cover provider-side contracts only. If the role is not Provider, standards coverage is not applied and the To confirm line says so.</t>
+          <t>The Start2 entity in this contract. Guessed from the entity list and the text when not obvious.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Role basis</t>
+          <t>Our role</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>One sentence on why that role was chosen. Always filled when the role was guessed.</t>
+          <t>Provider, Buyer or Other. The standards cover provider-side contracts only. If the role is not Provider, standards coverage is not applied and the To confirm line says so.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Counterparty</t>
+          <t>Role basis</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>The other party.</t>
+          <t>One sentence on why that role was chosen. Always filled when the role was guessed.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Critical / High / Medium / Low</t>
+          <t>Counterparty</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Formulas: number of Findings at each severity.</t>
+          <t>The other party.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>To confirm</t>
+          <t>Critical / High / Medium / Low</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Formula: the number of Critical and High findings. These are logged for a person to confirm; nothing else is recommended.</t>
+          <t>Formulas: number of Findings at each severity.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Documents not supplied</t>
+          <t>To confirm</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Formula: the number of rows on the Documents not supplied sheet.</t>
+          <t>Formula: the number of Critical and High findings. These are logged for a person to confirm; nothing else is recommended.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Review lead time</t>
+          <t>Documents not supplied</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Formula from Whose paper.</t>
+          <t>Formula: the number of rows on the Documents not supplied sheet.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Sign-off chain</t>
+          <t>Review lead time</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Fixed. Every contract goes to all three approvers in order.</t>
+          <t>Formula from Whose paper.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>Sign-off chain</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Fixed. Every contract goes to all three approvers in order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>Key facts (Fact / Value / Where)</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Facts used in the review: parties, dates, amounts, law, forum, language, annexes, with arithmetic checks. Where gives the contract reference and page.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sheet: Findings (one row per issue)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Running number.</t>
-        </is>
-      </c>
+      <c r="B35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Critical, High, Medium or Low (drop-down).</t>
+          <t>Running number.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Missing, Partial or Deviant (a standard clause); Client: Reject, Escalate, Conditional or Accept (a client-added clause matched to the playbook); Unclassified clause (not in the standard or playbook, generic screen); Commercial (fee, dates, arithmetic); Execution (a failed check); Not supplied (a document that forms part of the contract was not supplied, so its terms were not reviewed); Other.</t>
+          <t>Critical, High, Medium or Low (drop-down).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Clause</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Standard clause ID (for example LOL), the playbook row name, or Check n.</t>
+          <t>Missing, Partial or Deviant (a standard clause); Client: Reject, Escalate, Conditional or Accept (a client-added clause matched to the playbook); Unclassified clause (not in the standard or playbook, generic screen); Commercial (fee, dates, arithmetic); Execution (a failed check); Not supplied (a document that forms part of the contract was not supplied, so its terms were not reviewed); Other.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>Clause</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Contract clause number and page, for example 13.1 (p. 10). 'Not in contract' for an absent clause.</t>
+          <t>Standard clause ID (for example LOL), the playbook row name, or Check n.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Quote</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Verbatim text from the contract: the full sentence or sub-clause, with the words the finding turns on in bold. '...' marks text left out between excerpts. Scanned contracts are transcribed from page images, so check the page before relying on a quote.</t>
+          <t>Contract clause number and page, for example 13.1 (p. 10). 'Not in contract' for an absent clause.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Quote</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>What the clause says in plain words, what it means for Start2 in practice, how it compares with the Start2 standard, and why it has this severity.</t>
+          <t>Verbatim text from the contract: the full sentence or sub-clause, with the words the finding turns on in bold. '...' marks text left out between excerpts. Scanned contracts are transcribed from page images, so check the page before relying on a quote.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Issue</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>What to do next and who does it: what to check internally, what to ask the counterparty for, and a fallback if they decline.</t>
+          <t>What the clause says in plain words, what it means for Start2 in practice, how it compares with the Start2 standard, and why it has this severity. Low and no-action findings use two sentences.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Suggested language</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Wording to propose to the counterparty. For a standard clause, the Start2 standard language with the parties named as in this contract; otherwise wording written for this finding. Fill bracketed items and adjust before sending.</t>
+          <t>What to do next and who does it: what to check internally, what to ask the counterparty for, and a fallback if they decline. Low and no-action findings use one sentence.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Subjective</t>
+          <t>Suggested language</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Yes when the quoted text lets the counterparty alone judge Start2's work, payment or people. The severity already includes the one-level raise.</t>
+          <t>Wording to propose to the counterparty. For a standard clause, the Start2 standard language with the parties named as in this contract; otherwise wording written for this finding. Fill bracketed items and adjust before sending.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t>Subjective</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Yes when the quoted text lets the counterparty alone judge Start2's work, payment or people. The severity already includes the one-level raise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
           <t>Action needed</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>No when the finding needs nothing beyond noting it. The severity already includes the one-level reduction.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Sheet: Coverage (one row per standard clause)</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Stable clause key from the standards workbook.</t>
-        </is>
-      </c>
+      <c r="B47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Clause</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Clause name.</t>
+          <t>Stable clause key from the standards workbook.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Base severity</t>
+          <t>Clause</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Severity if the clause is missing or deviant. Editable for this contract (for example raise anti-bribery to Medium for a government counterparty). n/a for internal rules.</t>
+          <t>Clause name.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Verdict</t>
+          <t>Base severity</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Conforming, Partial, Deviant, Missing, Not supplied (the contract says the topic is governed by a document that was not supplied), or N/A (drop-down).</t>
+          <t>Severity if the clause is missing or deviant. Editable for this contract (for example raise anti-bribery to Medium for a government counterparty). n/a for internal rules.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>Verdict</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Contract clause number and page where the clause was found.</t>
+          <t>Conforming, Partial, Deviant, Missing, Not supplied (the contract says the topic is governed by a document that was not supplied), or N/A (drop-down).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Severity</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Formula. Missing, Deviant or Not supplied = Base severity; Partial = one level lower (floor Low); Conforming or N/A = '-'.</t>
+          <t>Contract clause number and page where the clause was found.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Formula. Missing, Deviant or Not supplied = Base severity; Partial = one level lower (floor Low); Conforming or N/A = '-'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>One line on what is present or absent. Details are in Findings.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Sheet: Checks (one row per execution check)</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Number of the check in the standards workbook.</t>
-        </is>
-      </c>
+      <c r="B55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>What is verified before a draft leaves Start2 and again before signature.</t>
+          <t>Number of the check in the standards workbook.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Pass, Fail, N/A or Cannot verify (drop-down).</t>
+          <t>What is verified before a draft leaves Start2 and again before signature.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Pass, Fail, N/A or Cannot verify (drop-down).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>What was seen, with page references.</t>
         </is>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Documents not supplied (one row per document)</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Clauses to correct</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>The document as the contract names it, with version or date if given.</t>
+          <t>For a failed check, each contract clause or page that needs correcting and what to change, numbered.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Referenced at</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Every contract clause and page where the document is named, numbered.</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Documents not supplied (one row per document)</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Quotes</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>The contract text at each of those places, numbered to match, with the document's name in bold.</t>
+          <t>The document as the contract names it, with version or date if given.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Part of contract</t>
+          <t>Referenced at</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Yes when the contract says the document applies to or forms part of the contract. Those also appear in Findings as type Not supplied.</t>
+          <t>Every contract clause and page where the document is named, numbered.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Governs</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>What the contract says or shows the document covers. Never a guess at its content.</t>
+          <t>The contract text at each of those places, numbered to match, with the document's name in bold.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Effect on this review</t>
+          <t>Part of contract</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Which findings and coverage rows could not be completed without it.</t>
+          <t>Yes when the contract says the document applies to or forms part of the contract. Those also appear in Findings as type Not supplied.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Governs</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>How to obtain it and what to check once it is in hand.</t>
+          <t>What the contract says or shows the document covers. Never a guess at its content.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Terms used</t>
+          <t>Effect on this review</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Where a legal term or a Start2 clause code (for example WARR) is used without explanation, a 'Terms used' line at the end of the cell gives its plain meaning.</t>
+          <t>Which findings and coverage rows could not be completed without it.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Rules</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n"/>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>How to obtain it and what to check once it is in hand.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Counts</t>
+          <t>Terms used</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
+          <t>Where a legal term or a Start2 clause code (for example WARR) is used without explanation, a 'Terms used' line at the end of the cell gives its plain meaning.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>The role is guessed when unclear and recorded on Summary. The only time the skill asks is when a name containing 'Start2' other than Start2 Asia appears: it flags the name and waits for confirmation.</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
+          <t>Counts</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Role and intake</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Before the review, the skill sends one intake message asking the requester to confirm the Start2 entity and role, send any documents the contract names but that were not supplied, and state the purpose. It does not stop again after that.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
           <t>Not legal advice</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>A screen against Start2 standards. Decisions follow the sign-off chain.</t>
         </is>
@@ -1403,13 +1427,13 @@
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1421,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1503,34 +1527,34 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Standards version</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Standards version</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Our side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Our entity</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Our role</t>
+          <t>Our entity</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -1539,7 +1563,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Role basis</t>
+          <t>Our role</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
@@ -1548,77 +1572,74 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Counterparty</t>
+          <t>Role basis</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="B15" s="7">
+      <c r="B16" s="7">
         <f>COUNTIF(Findings!$B$2:$B$300,"Critical")</f>
         <v/>
       </c>
-      <c r="C15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="C16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B16" s="7">
+      <c r="B17" s="7">
         <f>COUNTIF(Findings!$B$2:$B$300,"High")</f>
         <v/>
       </c>
-      <c r="C16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="C17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B17" s="7">
+      <c r="B18" s="7">
         <f>COUNTIF(Findings!$B$2:$B$300,"Medium")</f>
         <v/>
       </c>
-      <c r="C17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="C18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B18" s="7">
+      <c r="B19" s="7">
         <f>COUNTIF(Findings!$B$2:$B$300,"Low")</f>
-        <v/>
-      </c>
-      <c r="C18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-      <c r="B19" s="5">
-        <f>IF(B11="","",IF(B11&lt;&gt;"Provider","Not assessed: the standards cover provider-side contracts only",(B15+B16)&amp;" Critical and High findings to confirm"))</f>
         <v/>
       </c>
       <c r="C19" s="5" t="n"/>
@@ -1626,11 +1647,11 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Documents not supplied</t>
+          <t>To confirm</t>
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTA('Documents not supplied'!$B$2:$B$300)</f>
+        <f>IF(B12="","",IF(B12&lt;&gt;"Provider","Not assessed: the standards cover provider-side contracts only",(B16+B17)&amp;" Critical and High findings to confirm"))</f>
         <v/>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -1638,11 +1659,11 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Review lead time</t>
+          <t>Documents not supplied</t>
         </is>
       </c>
       <c r="B21" s="5">
-        <f>IF(B7="","",IF(B7="Start2 template, unmodified","3 business days","5 business days"))</f>
+        <f>COUNTA('Documents not supplied'!$B$2:$B$300)</f>
         <v/>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -1650,27 +1671,39 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>Review lead time</t>
+        </is>
+      </c>
+      <c r="B22" s="5">
+        <f>IF(B7="","",IF(B7="Start2 template, unmodified","3 business days","5 business days"))</f>
+        <v/>
+      </c>
+      <c r="C22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>Sign-off chain</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>1. Director of People and Operations; 2. Regional Director of Innovation and Product Strategy; 3. CEO. Applies to every contract.</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="C23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Key facts</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A15:A18">
+  <conditionalFormatting sqref="A16:A19">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Critical"</formula>
     </cfRule>
@@ -1684,7 +1717,7 @@
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Draft,Executed"</formula1>
     </dataValidation>
@@ -1694,8 +1727,11 @@
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Start2 template, unmodified,Start2 template, modified,Client or third-party paper"</formula1>
     </dataValidation>
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Provider,Buyer,Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Pre-signature,Signed,Renewal"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2734,13 +2770,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2764,6 +2801,11 @@
           <t>Evidence</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clauses to correct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="n">
@@ -2776,6 +2818,7 @@
       </c>
       <c r="C2" s="5" t="n"/>
       <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -2788,6 +2831,7 @@
       </c>
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -2800,6 +2844,7 @@
       </c>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -2812,6 +2857,7 @@
       </c>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -2824,6 +2870,7 @@
       </c>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -2836,6 +2883,7 @@
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -2848,6 +2896,7 @@
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -2860,6 +2909,7 @@
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -2872,6 +2922,7 @@
       </c>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -2884,6 +2935,7 @@
       </c>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -2896,6 +2948,7 @@
       </c>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -2908,6 +2961,7 @@
       </c>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
+++ b/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Critical, High, Medium or Low (drop-down).</t>
+          <t>Critical, High, Medium or Low (drop-down). A comment on the cell explains a severity that differs from the usual rule.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>What the clause says in plain words, what it means for Start2 in practice, how it compares with the Start2 standard, and why it has this severity. Low and no-action findings use two sentences.</t>
+          <t>What the clause says in plain words, what it means for Start2 in practice, and how it compares with the Start2 standard. Low and no-action findings use two sentences.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Wording to propose to the counterparty. For a standard clause, the Start2 standard language with the parties named as in this contract; otherwise wording written for this finding. Fill bracketed items and adjust before sending.</t>
+          <t>Wording to propose to the counterparty. For a standard clause, the Start2 standard language with the parties named as in this contract; otherwise wording written for this finding.</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Where a legal term or a Start2 clause code (for example WARR) is used without explanation, a 'Terms used' line at the end of the cell gives its plain meaning.</t>
+          <t>When plain-language explanations were requested at intake, a legal term or a Start2 clause code (for example WARR) used without explanation gets a 'Terms used' line at the end of the cell giving its plain meaning.</t>
         </is>
       </c>
     </row>

--- a/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
+++ b/skills/contract-review-flagger/templates/Contract_Review_Template.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Documents not supplied" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Coverage'!$A$1:$G$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Documents not supplied'!$A$1:$H$2</definedName>
   </definedNames>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>A finding that needs nothing from Start2 beyond noting it is lowered one severity level and marked No in the Action needed column. Its Action explains why nothing is needed.</t>
+          <t>A finding that needs nothing from Start2 beyond noting it is lowered one severity level. Its Action starts 'No action needed' and says why.</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>A finding whose quoted text lets the counterparty alone judge Start2's work, payment or people (for example 'acceptable to Canada', 'to the satisfaction of', 'in its sole discretion') is raised one severity level and marked Yes in the Subjective column.</t>
+          <t>A finding whose quoted text lets the counterparty alone judge Start2's work, payment or people (for example 'acceptable to Canada', 'to the satisfaction of', 'in its sole discretion') is raised one severity level. The judging words are in bold in the Quote.</t>
         </is>
       </c>
     </row>
@@ -1092,332 +1092,308 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Subjective</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Yes when the quoted text lets the counterparty alone judge Start2's work, payment or people. The severity already includes the one-level raise.</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Coverage (one row per standard clause)</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Action needed</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>No when the finding needs nothing beyond noting it. The severity already includes the one-level reduction.</t>
+          <t>Stable clause key from the standards workbook.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Coverage (one row per standard clause)</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Clause</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Clause name.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Base severity</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Stable clause key from the standards workbook.</t>
+          <t>Severity if the clause is missing or deviant. Editable for this contract (for example raise anti-bribery to Medium for a government counterparty). n/a for internal rules.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Clause</t>
+          <t>Verdict</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Clause name.</t>
+          <t>Conforming, Partial, Deviant, Missing, Not supplied (the contract says the topic is governed by a document that was not supplied), or N/A (drop-down).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Base severity</t>
+          <t>Where</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Severity if the clause is missing or deviant. Editable for this contract (for example raise anti-bribery to Medium for a government counterparty). n/a for internal rules.</t>
+          <t>Contract clause number and page where the clause was found.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Verdict</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Conforming, Partial, Deviant, Missing, Not supplied (the contract says the topic is governed by a document that was not supplied), or N/A (drop-down).</t>
+          <t>Formula. Missing, Deviant or Not supplied = Base severity; Partial = one level lower (floor Low); Conforming or N/A = '-'.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Where</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Contract clause number and page where the clause was found.</t>
+          <t>One line on what is present or absent. Details are in Findings.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Formula. Missing, Deviant or Not supplied = Base severity; Partial = one level lower (floor Low); Conforming or N/A = '-'.</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Checks (one row per execution check)</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>One line on what is present or absent. Details are in Findings.</t>
+          <t>Number of the check in the standards workbook.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Checks (one row per execution check)</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n"/>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>What is verified before a draft leaves Start2 and again before signature.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Result</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Number of the check in the standards workbook.</t>
+          <t>Pass, Fail, N/A or Cannot verify (drop-down).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>What is verified before a draft leaves Start2 and again before signature.</t>
+          <t>What was seen, with page references.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Result</t>
+          <t>Clauses to correct</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Pass, Fail, N/A or Cannot verify (drop-down).</t>
+          <t>For a failed check, each contract clause or page that needs correcting and what to change, numbered.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>What was seen, with page references.</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Sheet: Documents not supplied (one row per document)</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Clauses to correct</t>
+          <t>Document</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>For a failed check, each contract clause or page that needs correcting and what to change, numbered.</t>
+          <t>The document as the contract names it, with version or date if given.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Sheet: Documents not supplied (one row per document)</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n"/>
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Referenced at</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Every contract clause and page where the document is named, numbered.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Quotes</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>The document as the contract names it, with version or date if given.</t>
+          <t>The contract text at each of those places, numbered to match, with the document's name in bold.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Referenced at</t>
+          <t>Part of contract</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Every contract clause and page where the document is named, numbered.</t>
+          <t>Yes when the contract says the document applies to or forms part of the contract. Those also appear in Findings as type Not supplied.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Quotes</t>
+          <t>Governs</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>The contract text at each of those places, numbered to match, with the document's name in bold.</t>
+          <t>What the contract says or shows the document covers. Never a guess at its content.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Part of contract</t>
+          <t>Effect on this review</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Yes when the contract says the document applies to or forms part of the contract. Those also appear in Findings as type Not supplied.</t>
+          <t>Which findings and coverage rows could not be completed without it.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Governs</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>What the contract says or shows the document covers. Never a guess at its content.</t>
+          <t>How to obtain it and what to check once it is in hand.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Effect on this review</t>
+          <t>Terms used</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Which findings and coverage rows could not be completed without it.</t>
+          <t>When plain-language explanations were requested at intake, a legal term or a Start2 clause code (for example WARR) used without explanation gets a 'Terms used' line at the end of the cell giving its plain meaning.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>How to obtain it and what to check once it is in hand.</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Terms used</t>
+          <t>Counts</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>When plain-language explanations were requested at intake, a legal term or a Start2 clause code (for example WARR) used without explanation gets a 'Terms used' line at the end of the cell giving its plain meaning.</t>
+          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Rules</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="n"/>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Role and intake</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Before the review, the skill sends one intake message asking the requester to confirm the Start2 entity and role, send any documents the contract names but that were not supplied, and state the purpose. It does not stop again after that.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Counts</t>
+          <t>Not legal advice</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Counts and the to-confirm line use the Findings sheet only. Coverage severity is a view and is not counted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>Role and intake</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Before the review, the skill sends one intake message asking the requester to confirm the Start2 entity and role, send any documents the contract names but that were not supplied, and state the purpose. It does not stop again after that.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Not legal advice</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>A screen against Start2 standards. Decisions follow the sign-off chain.</t>
         </is>
@@ -1427,12 +1403,12 @@
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1744,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1756,8 +1732,6 @@
     <col width="70" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1806,19 +1780,9 @@
           <t>Suggested language</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Subjective</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Action needed</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:I2"/>
   <conditionalFormatting sqref="B2:B300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Critical"</formula>
@@ -1833,18 +1797,12 @@
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="2">
     <dataValidation sqref="B2:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Missing,Partial,Deviant,Client: Reject,Client: Escalate,Client: Conditional,Client: Accept,Unclassified clause,Commercial,Execution,Not supplied,Other"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
